--- a/model_results/analysis_summaries.xlsx
+++ b/model_results/analysis_summaries.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1964,13 +1964,135 @@
           <t>10_22_2026-07_46_app_[64, 128, 64]_0_True_256_500_50_False_results_file.txt</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="P25" t="b">
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0.1748345879176053</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>app_inhibition</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[64, 128, 256, 384, 256, 128, 64]</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>60</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>256</v>
+      </c>
+      <c r="H26" t="n">
+        <v>500</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.6148678907299597</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.4990147783251231</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>10_22_2026-18_26</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>10_22_2026-18_26_app_[64, 128, 256, 384, 256, 128, 64]_0_True_256_500_60_True_results_file.txt</t>
+        </is>
+      </c>
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.08306873397382432</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>app_inhibition</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[64, 128, 256, 384, 256, 128, 64]</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>50</v>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>128</v>
+      </c>
+      <c r="H27" t="n">
+        <v>500</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6838334079713391</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>10_22_2026-18_35</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>10_22_2026-18_35_app_[64, 128, 256, 384, 256, 128, 64]_0_True_128_500_50_True_results_file.txt</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.07013354728470822</v>
       </c>
     </row>
   </sheetData>
